--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -831,31 +831,33 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46204</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>180.28391146199303</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>519.71608853800694</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>8471.2997110135693</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>1528.7002889864307</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1125,7 +1127,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1195,7 +1197,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8991.0157995515765</v>
+        <v>8471.2997110135693</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1230,7 +1232,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1008.9842004484235</v>
+        <v>1528.7002889864307</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -865,31 +865,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46211</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>169.86279204898605</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>530.13720795101392</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>7941.1625030625555</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>2058.8374969374445</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1127,7 +1129,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1162,7 +1164,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9800</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1197,7 +1199,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8471.2997110135693</v>
+        <v>7941.1625030625555</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1232,7 +1234,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1528.7002889864307</v>
+        <v>2058.8374969374445</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -796,7 +796,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
-        <v>46197</v>
+        <v>46196</v>
       </c>
       <c r="B3" s="23">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
@@ -832,7 +832,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
-        <v>46204</v>
+        <v>46174</v>
       </c>
       <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
@@ -899,31 +899,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46218</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>159.23271291313185</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>540.76728708686812</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>7400.3952159756873</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>2599.6047840243127</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -931,31 +933,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46225</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>148.38948408557562</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>551.61051591442435</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>6848.7847000612628</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>3151.2152999387372</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1129,7 +1133,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1164,7 +1168,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9100</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1199,7 +1203,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7941.1625030625555</v>
+        <v>6848.7847000612628</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1234,7 +1238,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2058.8374969374445</v>
+        <v>3151.2152999387372</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -969,31 +969,33 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
+      <c r="A8" s="2">
+        <v>46232</v>
+      </c>
+      <c r="B8" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>137.328831582042</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
+        <v>562.67116841795803</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>6286.1135316433047</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>3713.8864683566953</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1004,31 +1006,33 @@
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46239</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>126.0463957181946</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>573.95360428180538</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>5712.1599273614993</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>4287.8400726385007</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1168,7 +1172,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>7700</v>
+        <v>6300</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1203,7 +1207,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>6848.7847000612628</v>
+        <v>5712.1599273614993</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1238,7 +1242,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3151.2152999387372</v>
+        <v>4287.8400726385007</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -1043,31 +1043,33 @@
       <c r="L9" s="24"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>114.53772939121589</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>585.46227060878414</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>5126.6976567527154</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>4873.3023432472846</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1077,31 +1079,33 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46254</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>102.79829632693014</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>597.20170367306991</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>4529.4959530796459</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>5470.5040469203541</v>
       </c>
       <c r="J11" s="14"/>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>6300</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1207,7 +1211,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>5712.1599273614993</v>
+        <v>4529.4959530796459</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1242,7 +1246,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4287.8400726385007</v>
+        <v>5470.5040469203541</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Reena_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Reena_Weekly.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Loan1" sheetId="5" r:id="rId1"/>
+    <sheet name="187" sheetId="5" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -791,7 +791,7 @@
    "-" &amp; K3 &amp;
    "-N" &amp; RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1))),
    "")</f>
-        <v>L10000W17-Reena-NLoan1</v>
+        <v>L10000W17-Reena-N187</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -1110,108 +1110,114 @@
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
+      <c r="A12" s="2">
+        <v>46261</v>
+      </c>
+      <c r="B12" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>90.823469291778352</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
+        <v>609.17653070822166</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3920.3194223714245</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>6079.6805776285755</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="23" t="str">
+      <c r="A13" s="19">
+        <v>46268</v>
+      </c>
+      <c r="B13" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>78.608528268940589</v>
+      </c>
+      <c r="F13" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
+        <v>621.39147173105937</v>
+      </c>
+      <c r="G13" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3298.927950640365</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>6701.0720493596345</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>23</v>
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>4900</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="22" t="str">
+      <c r="A14" s="2">
+        <v>46274</v>
+      </c>
+      <c r="B14" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="1" t="str">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>66.148658597886595</v>
+      </c>
+      <c r="F14" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G14" s="1" t="str">
+        <v>633.85134140211335</v>
+      </c>
+      <c r="G14" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H14" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>2665.0766092382519</v>
+      </c>
+      <c r="H14" s="1">
+        <f t="shared" si="2"/>
+        <v>7334.9233907617481</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>22</v>
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>4529.4959530796459</v>
+        <v>2665.0766092382519</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1246,7 +1252,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>5470.5040469203541</v>
+        <v>7334.9233907617481</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
